--- a/reports/devops-jobs-israel-2026-W37.xlsx
+++ b/reports/devops-jobs-israel-2026-W37.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07T12:18:12</t>
+    <t xml:space="preserve">2026-09-08T11:07:21</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -528,825 +528,903 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4464322474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4464480350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senior devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NextSilicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4461838137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-production-engineering-at-confidential-4452985368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comply365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
+  </si>
+  <si>
     <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
   </si>
   <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zipher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator / DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4464090264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4461447149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-horizon-technologies-ltd-4462294494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-qb-systems-ltd-4461731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
   </si>
   <si>
     <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4464322474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4462918971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4461447149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comply365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4464038315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4462202153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4461838137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wonderful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-production-engineering-at-confidential-4452985368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer ( Kafka Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-kafka-oriented-at-nuvei-4464020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4459946559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVeye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
     <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">North District, Israel</t>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux/Windows System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-windows-system-administrator-at-webox-ltd-4461811690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1368,7 +1446,7 @@
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1520,7 +1598,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1528,7 +1606,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1536,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1544,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="10">
@@ -1616,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1643,20 +1721,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3">
         <v>9</v>
@@ -1664,23 +1742,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>415</v>
+        <v>467</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1699,130 +1777,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>444</v>
+        <v>350</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>349</v>
+        <v>470</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>343</v>
+        <v>473</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>448</v>
+        <v>366</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>449</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>340</v>
+        <v>475</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1847,13 +1925,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
@@ -1864,10 +1942,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>31.3</v>
+        <v>23.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1876,88 +1954,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.4</v>
+        <v>29.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.2</v>
+        <v>19.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1969,7 +2047,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2041,7 +2119,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -2073,7 +2151,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2105,7 +2183,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -2137,7 +2215,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2169,7 +2247,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2201,7 +2279,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2233,7 +2311,7 @@
         <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2265,7 +2343,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -2297,7 +2375,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2329,7 +2407,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2361,7 +2439,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2393,7 +2471,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -2425,7 +2503,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -2457,7 +2535,7 @@
         <v>95</v>
       </c>
       <c r="J15" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -2489,7 +2567,7 @@
         <v>101</v>
       </c>
       <c r="J16" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -2521,7 +2599,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -2553,7 +2631,7 @@
         <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2585,7 +2663,7 @@
         <v>91</v>
       </c>
       <c r="J19" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -2617,7 +2695,7 @@
         <v>117</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2649,7 +2727,7 @@
         <v>120</v>
       </c>
       <c r="J21" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -2681,7 +2759,7 @@
         <v>126</v>
       </c>
       <c r="J22" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -2713,7 +2791,7 @@
         <v>62</v>
       </c>
       <c r="J23" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -2745,7 +2823,7 @@
         <v>136</v>
       </c>
       <c r="J24" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -2777,7 +2855,7 @@
         <v>141</v>
       </c>
       <c r="J25" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -2809,7 +2887,7 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2841,7 +2919,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -2873,7 +2951,7 @@
         <v>76</v>
       </c>
       <c r="J28" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2905,7 +2983,7 @@
         <v>159</v>
       </c>
       <c r="J29" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2937,7 +3015,7 @@
         <v>147</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2967,7 +3045,7 @@
         <v>168</v>
       </c>
       <c r="J31" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2984,7 +3062,7 @@
         <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
@@ -2994,78 +3072,78 @@
         <v>172</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>171</v>
@@ -3074,61 +3152,61 @@
         <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
@@ -3141,10 +3219,10 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="J37" s="3">
         <v>0</v>
@@ -3155,10 +3233,10 @@
         <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
@@ -3171,24 +3249,24 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>51</v>
+        <v>189</v>
       </c>
       <c r="J38" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
@@ -3201,81 +3279,81 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="J40" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>171</v>
@@ -3284,34 +3362,34 @@
         <v>43</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3321,70 +3399,70 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3392,7 +3470,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>212</v>
@@ -3414,24 +3492,24 @@
         <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="J46" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>37</v>
@@ -3441,21 +3519,21 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="J47" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>171</v>
@@ -3471,57 +3549,57 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>48</v>
@@ -3531,24 +3609,24 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="J50" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>43</v>
@@ -3561,72 +3639,70 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>233</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="J53" s="3">
         <v>1</v>
@@ -3634,13 +3710,13 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>133</v>
@@ -3653,51 +3729,51 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>171</v>
@@ -3713,10 +3789,10 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3724,13 +3800,13 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>133</v>
@@ -3743,24 +3819,24 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="J57" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>248</v>
+        <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
@@ -3773,87 +3849,87 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="J59" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>189</v>
+        <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>48</v>
@@ -3863,10 +3939,10 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3874,78 +3950,76 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>262</v>
+        <v>43</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J63" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -3955,27 +4029,27 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="J64" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>48</v>
@@ -3985,21 +4059,21 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="J65" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>47</v>
+        <v>264</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>171</v>
@@ -4015,27 +4089,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="J66" s="3">
-        <v>4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4045,27 +4119,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>147</v>
+        <v>271</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>48</v>
@@ -4075,21 +4149,21 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J68" s="3">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>171</v>
@@ -4098,31 +4172,31 @@
         <v>43</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="J69" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>189</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>43</v>
@@ -4135,21 +4209,21 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J70" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>171</v>
@@ -4165,27 +4239,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>262</v>
+        <v>43</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>48</v>
@@ -4195,21 +4269,21 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="J72" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>92</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>171</v>
@@ -4218,34 +4292,34 @@
         <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>294</v>
+        <v>176</v>
       </c>
       <c r="J73" s="3">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>37</v>
@@ -4255,40 +4329,40 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>298</v>
+        <v>46</v>
       </c>
       <c r="J74" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>47</v>
+        <v>292</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>299</v>
+        <v>186</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="J75" s="3">
         <v>0</v>
@@ -4296,40 +4370,40 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="J76" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>171</v>
@@ -4340,34 +4414,32 @@
       <c r="E77" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>306</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>189</v>
+        <v>299</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>308</v>
+        <v>214</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4377,40 +4449,40 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>310</v>
+        <v>176</v>
       </c>
       <c r="J78" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="J79" s="3">
         <v>22</v>
@@ -4418,43 +4490,43 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>262</v>
+        <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="J80" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>175</v>
+        <v>307</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>133</v>
@@ -4462,58 +4534,56 @@
       <c r="E81" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>233</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>311</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>43</v>
+        <v>312</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="J82" s="3">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>324</v>
+        <v>203</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>171</v>
@@ -4529,27 +4599,27 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>120</v>
+        <v>317</v>
       </c>
       <c r="J83" s="3">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>329</v>
+        <v>171</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
@@ -4559,54 +4629,56 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J85" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
@@ -4619,17 +4691,357 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="I90" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J90" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="J86" s="3">
-        <v>43</v>
+      <c r="B91" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J92" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J93" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J96" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J97" s="3">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4716,6 +5128,17 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4723,8 +5146,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4757,51 +5180,51 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4809,18 +5232,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4828,18 +5251,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4847,18 +5270,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4866,15 +5289,15 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>171</v>
@@ -4885,18 +5308,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4904,18 +5327,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4923,18 +5346,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4942,18 +5365,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -4961,18 +5384,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -4980,18 +5403,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>156</v>
+        <v>292</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -4999,18 +5422,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>299</v>
+        <v>214</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5023,10 +5446,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>304</v>
+        <v>169</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>171</v>
@@ -5037,11 +5460,125 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G22"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5058,6 +5595,12 @@
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5071,15 +5614,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>233</v>
+        <v>330</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5087,7 +5630,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5095,7 +5638,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5103,7 +5646,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
         <v>20</v>
@@ -5111,7 +5654,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5119,7 +5662,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5127,7 +5670,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5135,7 +5678,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5143,15 +5686,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5159,15 +5702,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>129</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5175,7 +5718,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5183,7 +5726,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5191,7 +5734,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5213,7 +5756,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5226,15 +5769,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5242,7 +5785,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5250,7 +5793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5258,7 +5801,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5266,15 +5809,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5282,7 +5825,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5290,7 +5833,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5298,7 +5841,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5306,34 +5849,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5351,16 +5894,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5466,13 +6009,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5480,10 +6023,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -5494,13 +6037,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5508,13 +6051,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5522,13 +6065,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5536,10 +6079,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5550,10 +6093,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C15" s="3">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -5564,10 +6107,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3">
-        <v>2.0</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -5590,21 +6133,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -5612,10 +6155,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4">
@@ -5623,10 +6166,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5645,7 +6188,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5653,7 +6196,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -5661,28 +6204,28 @@
         <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5690,15 +6233,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>123</v>
+        <v>312</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5712,7 +6255,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -5725,10 +6268,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5740,10 +6283,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5760,28 +6303,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>87</v>
@@ -5792,31 +6335,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>368</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>372</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -5824,31 +6367,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>136</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
@@ -5856,31 +6399,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="F5" s="3">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -5888,31 +6431,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>399</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>401</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="F6" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>39</v>
+        <v>403</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -5920,31 +6463,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -5952,31 +6495,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -5984,31 +6527,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>392</v>
+        <v>165</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -6016,31 +6559,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>327</v>
+        <v>416</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="F10" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -6048,31 +6591,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>402</v>
+        <v>171</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>80</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12">
@@ -6080,31 +6623,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>165</v>
+        <v>427</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -6112,31 +6655,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>412</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -6144,31 +6687,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F14" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -6176,31 +6719,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>327</v>
+        <v>439</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>180</v>
+        <v>441</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -6208,31 +6751,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>186</v>
+        <v>444</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
@@ -6240,31 +6783,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>426</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -6272,31 +6815,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>429</v>
+        <v>193</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>402</v>
+        <v>205</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="F18" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -6304,31 +6847,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>171</v>
+        <v>456</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20">
@@ -6336,28 +6879,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>327</v>
+        <v>459</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>329</v>
+        <v>55</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>330</v>
+        <v>461</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>46</v>
@@ -6368,31 +6911,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>171</v>
+        <v>441</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>87</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W37.xlsx
+++ b/reports/devops-jobs-israel-2026-W37.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08T11:07:21</t>
+    <t xml:space="preserve">2026-09-09T11:12:04</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -198,222 +198,213 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8161565&amp;gh_jid=8161565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8161565&amp;gh_jid=8161565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
@@ -528,184 +519,553 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463554987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBX Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4464322474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wonderful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senior devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
   </si>
   <si>
     <t xml:space="preserve">Wix</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4464480350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QualiGate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-qualigate-4462502196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terra Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NextSilicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4463579042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer ( Kafka Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-kafka-oriented-at-nuvei-4464020782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comply365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
     <t xml:space="preserve">Eitan Medical</t>
@@ -714,82 +1074,34 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextSilicon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4461838137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
   </si>
   <si>
     <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
@@ -801,417 +1113,168 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
   </si>
   <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-production-engineering-at-confidential-4452985368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comply365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator / DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4464090264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4461447149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-horizon-technologies-ltd-4462294494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-qb-systems-ltd-4461731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
@@ -1248,27 +1311,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -1314,112 +1383,34 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator - 243425</t>
   </si>
   <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1431,12 +1422,12 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -1446,7 +1437,13 @@
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1598,7 +1595,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1606,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1614,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1622,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1005</v>
+        <v>990</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1691,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1702,7 +1699,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1721,36 +1718,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1758,7 +1755,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1777,130 +1774,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>473</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>474</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>471</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>472</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>364</v>
+        <v>473</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1925,13 +1922,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2">
@@ -1939,13 +1936,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>23.8</v>
+        <v>12.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1954,88 +1951,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>34.2</v>
+        <v>36.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>29.5</v>
+        <v>34.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.6</v>
+        <v>17.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.6</v>
+        <v>21.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2046,7 +2043,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2119,7 +2116,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -2151,7 +2148,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2183,7 +2180,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -2215,7 +2212,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -2247,7 +2244,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -2255,63 +2252,63 @@
         <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="J7" s="3">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J8" s="3">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2319,10 +2316,10 @@
         <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>43</v>
@@ -2331,16 +2328,16 @@
         <v>48</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" s="3">
         <v>9</v>
@@ -2348,10 +2345,10 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -2375,15 +2372,15 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>43</v>
@@ -2395,27 +2392,27 @@
         <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J11" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>43</v>
@@ -2439,7 +2436,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -2447,7 +2444,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
@@ -2471,7 +2468,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -2479,7 +2476,7 @@
         <v>88</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>43</v>
@@ -2503,7 +2500,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -2511,10 +2508,10 @@
         <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2523,30 +2520,30 @@
         <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -2564,21 +2561,21 @@
         <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>43</v>
@@ -2587,19 +2584,19 @@
         <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J17" s="3">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2607,10 +2604,10 @@
         <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>43</v>
@@ -2619,19 +2616,19 @@
         <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="J18" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2639,10 +2636,10 @@
         <v>109</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>43</v>
@@ -2660,21 +2657,21 @@
         <v>112</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="J19" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>43</v>
@@ -2683,158 +2680,158 @@
         <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J21" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J22" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="J23" s="3">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J24" s="3">
-        <v>88</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>43</v>
@@ -2843,30 +2840,30 @@
         <v>48</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J25" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>43</v>
@@ -2875,19 +2872,19 @@
         <v>48</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
@@ -2895,51 +2892,51 @@
         <v>148</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J27" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
@@ -2948,18 +2945,18 @@
         <v>155</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="J28" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>43</v>
@@ -2971,30 +2968,30 @@
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="J29" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>43</v>
@@ -3002,34 +2999,32 @@
       <c r="E30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>37</v>
@@ -3039,48 +3034,48 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J32" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>173</v>
@@ -3089,10 +3084,10 @@
         <v>174</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3102,37 +3097,37 @@
         <v>175</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="J34" s="3">
         <v>6</v>
@@ -3140,13 +3135,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>43</v>
@@ -3159,27 +3154,27 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J35" s="3">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>37</v>
@@ -3189,27 +3184,27 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>37</v>
@@ -3219,87 +3214,87 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J39" s="3">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>48</v>
@@ -3309,24 +3304,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
@@ -3334,29 +3329,31 @@
       <c r="E41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="J41" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>43</v>
@@ -3369,57 +3366,57 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>48</v>
@@ -3429,13 +3426,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="J44" s="3">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45">
@@ -3443,10 +3440,10 @@
         <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>43</v>
@@ -3459,117 +3456,117 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>43</v>
+        <v>218</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
       <c r="J48" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>37</v>
@@ -3579,13 +3576,13 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3593,13 +3590,13 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>48</v>
@@ -3609,24 +3606,24 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>43</v>
@@ -3639,13 +3636,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3653,10 +3650,10 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>36</v>
@@ -3669,57 +3666,57 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3729,27 +3726,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="J54" s="3">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>48</v>
@@ -3759,24 +3756,24 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>43</v>
@@ -3789,43 +3786,43 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3833,10 +3830,10 @@
         <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
@@ -3849,10 +3846,10 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3860,16 +3857,16 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>257</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>37</v>
@@ -3879,27 +3876,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>48</v>
@@ -3909,57 +3906,59 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="J60" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
@@ -3969,10 +3968,10 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="J62" s="3">
         <v>1</v>
@@ -3980,46 +3979,46 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -4029,54 +4028,54 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="J65" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>265</v>
+        <v>167</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>43</v>
@@ -4089,27 +4088,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>267</v>
+        <v>83</v>
       </c>
       <c r="J66" s="3">
-        <v>89</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4119,27 +4118,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="J67" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>48</v>
@@ -4149,54 +4148,54 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="J68" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>43</v>
@@ -4209,27 +4208,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>120</v>
+        <v>293</v>
       </c>
       <c r="J70" s="3">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
@@ -4239,27 +4238,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>48</v>
@@ -4269,147 +4268,147 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>189</v>
+        <v>301</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>169</v>
+        <v>304</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>46</v>
+        <v>307</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>176</v>
+        <v>310</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>168</v>
+        <v>314</v>
       </c>
       <c r="J76" s="3">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>297</v>
+        <v>226</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
@@ -4419,27 +4418,27 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="J77" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>299</v>
+        <v>189</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4449,10 +4448,10 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J78" s="3">
         <v>0</v>
@@ -4460,106 +4459,106 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>47</v>
+        <v>319</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>301</v>
+        <v>173</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>275</v>
+        <v>36</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="J79" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>305</v>
+        <v>47</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
       <c r="J81" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>311</v>
+        <v>187</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>312</v>
+        <v>130</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4569,116 +4568,114 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="J82" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>203</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>317</v>
+        <v>170</v>
       </c>
       <c r="J83" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>167</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>321</v>
+        <v>47</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>323</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
@@ -4686,32 +4683,34 @@
       <c r="E86" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>37</v>
@@ -4721,327 +4720,259 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>329</v>
+        <v>186</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>330</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>41</v>
+        <v>344</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>171</v>
+        <v>346</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>330</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>336</v>
+        <v>215</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>338</v>
+        <v>217</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>312</v>
+        <v>218</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>345</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>349</v>
+        <v>201</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>350</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J96" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="J97" s="3">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J95"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5137,8 +5068,6 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5146,8 +5075,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5180,13 +5109,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5194,18 +5123,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5213,7 +5142,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
@@ -5221,10 +5150,10 @@
         <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5232,7 +5161,7 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
@@ -5240,10 +5169,10 @@
         <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5251,18 +5180,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>171</v>
+        <v>278</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5270,18 +5199,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>213</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>282</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5289,18 +5218,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>228</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5308,18 +5237,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>237</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>169</v>
+        <v>319</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5327,258 +5256,11 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5588,19 +5270,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5614,47 +5283,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>365</v>
+        <v>267</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5662,15 +5331,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5678,7 +5347,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5686,7 +5355,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5694,7 +5363,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>368</v>
+        <v>125</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5702,15 +5371,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>129</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5718,7 +5387,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5726,7 +5395,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5734,7 +5403,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5756,12 +5425,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5769,23 +5438,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5793,7 +5462,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5801,7 +5470,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5809,7 +5478,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5817,15 +5486,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5833,7 +5502,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5841,7 +5510,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5849,7 +5518,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5857,26 +5526,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5894,16 +5563,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5911,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3">
         <v>23.0</v>
@@ -5939,7 +5608,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3">
         <v>10.4</v>
@@ -5953,7 +5622,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -5967,13 +5636,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
-        <v>7.4</v>
+        <v>7.0</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5981,7 +5650,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3">
         <v>6.7</v>
@@ -5995,7 +5664,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -6009,7 +5678,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C9" s="3">
         <v>4.8</v>
@@ -6023,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -6037,7 +5706,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -6051,13 +5720,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.0</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6065,7 +5734,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6079,13 +5748,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6093,7 +5762,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
@@ -6107,13 +5776,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6133,21 +5802,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -6155,10 +5824,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -6166,10 +5835,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6188,7 +5857,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -6196,28 +5865,28 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>275</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6225,7 +5894,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6233,15 +5902,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>312</v>
+        <v>119</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>123</v>
+        <v>257</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6255,7 +5924,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -6268,10 +5937,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6283,10 +5952,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6303,31 +5972,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -6335,31 +6004,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>396</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>397</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F3" s="3">
+        <v>100</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -6367,31 +6036,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>392</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
@@ -6399,31 +6068,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>339</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>396</v>
+        <v>179</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>338</v>
+        <v>174</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F5" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -6431,31 +6100,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>400</v>
+        <v>342</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>401</v>
+        <v>174</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
@@ -6463,19 +6132,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>405</v>
+        <v>342</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>407</v>
@@ -6484,10 +6153,10 @@
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
@@ -6495,31 +6164,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F8" s="3">
+        <v>88</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F8" s="3">
-        <v>48</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9">
@@ -6527,31 +6196,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>413</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>415</v>
+        <v>39</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6559,31 +6228,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>418</v>
+        <v>174</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6591,31 +6260,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>171</v>
+        <v>417</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>425</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -6623,31 +6292,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>215</v>
+        <v>422</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -6655,31 +6324,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -6687,31 +6356,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F14" s="3">
+        <v>56</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="3">
-        <v>40</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -6719,31 +6388,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>439</v>
+        <v>341</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>441</v>
+        <v>346</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -6751,31 +6420,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>349</v>
+        <v>441</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -6783,31 +6452,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F17" s="3">
-        <v>28</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -6815,19 +6484,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>452</v>
@@ -6839,7 +6508,7 @@
         <v>453</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>277</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6847,31 +6516,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F19" s="3">
+        <v>44</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F19" s="3">
-        <v>27</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>458</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
@@ -6879,31 +6548,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F20" s="3">
+        <v>44</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -6911,31 +6580,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F21" s="3">
+        <v>40</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>466</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W37.xlsx
+++ b/reports/devops-jobs-israel-2026-W37.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09T11:12:04</t>
+    <t xml:space="preserve">2026-09-10T11:08:11</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -183,12 +183,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
+    <t xml:space="preserve">Platform Enablement &amp; Automation Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Payoneer</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8185359/?gh_jid=8185359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
   </si>
   <si>
@@ -198,6 +207,18 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Advocate</t>
   </si>
   <si>
@@ -213,1131 +234,1155 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
+    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8161565&amp;gh_jid=8161565</t>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463554987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBX Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senior devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comply365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terra Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer ( Kafka Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-kafka-oriented-at-nuvei-4464020782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure Team Leader- 243578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-team-leader-243578-at-experis-4463040596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NextSilicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463554987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBX Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QualiGate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-qualigate-4462502196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terra Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextSilicon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4463579042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer ( Kafka Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-kafka-oriented-at-nuvei-4464020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comply365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator / DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -1401,18 +1446,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1422,12 +1455,12 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -1438,12 +1471,6 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1595,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -1603,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1611,7 +1638,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1619,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10">
@@ -1691,7 +1718,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1699,7 +1726,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1718,46 +1745,54 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1774,103 +1809,103 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>478</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>383</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>482</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>471</v>
+        <v>378</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -1878,23 +1913,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>473</v>
+        <v>380</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>474</v>
+        <v>376</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -1922,13 +1957,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
@@ -1936,13 +1971,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1951,88 +1986,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>36.0</v>
+        <v>34.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.7</v>
+        <v>31.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.7</v>
+        <v>17.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2044,7 +2079,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2116,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -2148,7 +2183,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2180,7 +2215,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -2212,28 +2247,26 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>56</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
@@ -2244,50 +2277,50 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>43</v>
@@ -2296,62 +2329,62 @@
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>43</v>
@@ -2360,27 +2393,27 @@
         <v>48</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J10" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>43</v>
@@ -2392,27 +2425,27 @@
         <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>43</v>
@@ -2424,27 +2457,27 @@
         <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J12" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
@@ -2456,27 +2489,27 @@
         <v>48</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J13" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>43</v>
@@ -2488,30 +2521,30 @@
         <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J14" s="3">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2520,30 +2553,30 @@
         <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -2552,30 +2585,30 @@
         <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>44</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>43</v>
@@ -2584,30 +2617,30 @@
         <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J17" s="3">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>43</v>
@@ -2616,30 +2649,30 @@
         <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>43</v>
@@ -2648,30 +2681,30 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>43</v>
@@ -2680,59 +2713,59 @@
         <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="J20" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>43</v>
@@ -2741,129 +2774,129 @@
         <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J23" s="3">
-        <v>89</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="J24" s="3">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J25" s="3">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>43</v>
@@ -2872,126 +2905,126 @@
         <v>48</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>163</v>
+        <v>43</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>43</v>
@@ -2999,53 +3032,57 @@
       <c r="E30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>167</v>
@@ -3054,34 +3091,34 @@
         <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>43</v>
@@ -3094,87 +3131,87 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J35" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>37</v>
@@ -3184,27 +3221,27 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="J36" s="3">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>37</v>
@@ -3214,27 +3251,27 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>37</v>
@@ -3247,21 +3284,21 @@
         <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
@@ -3274,13 +3311,13 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="J39" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3294,66 +3331,64 @@
         <v>197</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>43</v>
@@ -3369,24 +3404,24 @@
         <v>205</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="J42" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>48</v>
@@ -3396,24 +3431,24 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>43</v>
@@ -3421,29 +3456,31 @@
       <c r="E44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="J44" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>43</v>
@@ -3456,27 +3493,27 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>48</v>
@@ -3486,13 +3523,13 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="J46" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
@@ -3500,10 +3537,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>43</v>
@@ -3516,24 +3553,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>224</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
@@ -3546,54 +3583,54 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>43</v>
@@ -3606,57 +3643,57 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="J50" s="3">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>48</v>
@@ -3666,40 +3703,40 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="J53" s="3">
         <v>2</v>
@@ -3707,16 +3744,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3726,24 +3763,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="J54" s="3">
-        <v>90</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>244</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>43</v>
@@ -3759,54 +3796,54 @@
         <v>245</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>242</v>
+        <v>149</v>
       </c>
       <c r="J56" s="3">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>48</v>
@@ -3816,57 +3853,57 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>47</v>
+        <v>251</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>37</v>
@@ -3876,27 +3913,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>259</v>
+        <v>58</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>48</v>
@@ -3906,72 +3943,70 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>267</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J62" s="3">
         <v>1</v>
@@ -3979,163 +4014,165 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>174</v>
+        <v>267</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>280</v>
+        <v>171</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="J66" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>43</v>
@@ -4148,24 +4185,24 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>287</v>
+        <v>94</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>43</v>
@@ -4178,237 +4215,237 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="J69" s="3">
-        <v>64</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>153</v>
+        <v>286</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J70" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>296</v>
+        <v>173</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>172</v>
+        <v>293</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>299</v>
+        <v>185</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="J72" s="3">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="J73" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>304</v>
+        <v>158</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J74" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>88</v>
+        <v>302</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>310</v>
+        <v>182</v>
       </c>
       <c r="J75" s="3">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="J76" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
@@ -4418,24 +4455,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="J77" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>43</v>
@@ -4448,73 +4485,73 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>318</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J80" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4522,10 +4559,10 @@
         <v>47</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>324</v>
+        <v>173</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>43</v>
@@ -4538,27 +4575,27 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4568,90 +4605,92 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>167</v>
+        <v>324</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="J84" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>47</v>
+        <v>329</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>330</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>266</v>
+        <v>198</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4661,10 +4700,10 @@
         <v>331</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="J85" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -4675,7 +4714,7 @@
         <v>333</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
@@ -4683,124 +4722,122 @@
       <c r="E86" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="I86" s="3" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>336</v>
+        <v>47</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>186</v>
+        <v>338</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>342</v>
+        <v>204</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>48</v>
@@ -4810,70 +4847,72 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="J90" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>352</v>
+        <v>204</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="J92" s="3">
         <v>23</v>
@@ -4881,78 +4920,76 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>187</v>
+        <v>352</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>177</v>
+        <v>354</v>
       </c>
       <c r="J93" s="3">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>358</v>
+        <v>177</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>359</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>37</v>
@@ -4962,17 +4999,167 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="I95" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J95" s="3">
-        <v>3</v>
+      <c r="B97" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J100" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J100"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5068,6 +5255,11 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5075,8 +5267,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5109,51 +5301,51 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>68</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5161,18 +5353,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5180,18 +5372,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5199,18 +5391,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5218,18 +5410,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5237,18 +5429,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>168</v>
+        <v>318</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5256,11 +5448,106 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5270,6 +5557,11 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5283,47 +5575,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>267</v>
+        <v>379</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5331,23 +5623,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5355,7 +5647,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5363,7 +5655,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5371,7 +5663,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5379,7 +5671,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5387,7 +5679,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5395,7 +5687,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5403,7 +5695,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5425,12 +5717,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5438,23 +5730,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>244</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5462,7 +5754,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5470,7 +5762,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5478,7 +5770,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5486,7 +5778,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5494,7 +5786,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5502,7 +5794,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5510,7 +5802,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5518,7 +5810,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5526,26 +5818,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>225</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5563,16 +5855,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -5580,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3">
         <v>23.0</v>
@@ -5594,10 +5886,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
-        <v>10.9</v>
+        <v>13.0</v>
       </c>
       <c r="D3" s="3">
         <v>3</v>
@@ -5608,10 +5900,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5622,10 +5914,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C5" s="3">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5636,13 +5928,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>10.1</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5650,7 +5942,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3">
         <v>6.7</v>
@@ -5664,13 +5956,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>140</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5678,13 +5970,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3">
-        <v>4.8</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5692,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -5706,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -5720,13 +6012,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3">
-        <v>3.0</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5734,7 +6026,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5748,7 +6040,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -5762,7 +6054,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
@@ -5776,7 +6068,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5802,21 +6094,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3">
@@ -5824,10 +6116,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -5835,10 +6127,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -5857,7 +6149,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
@@ -5865,23 +6157,23 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -5894,23 +6186,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5937,10 +6229,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5952,10 +6244,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5972,31 +6264,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -6004,31 +6296,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4">
@@ -6036,31 +6328,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>296</v>
+        <v>173</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -6068,31 +6360,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
@@ -6100,31 +6392,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3">
         <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
@@ -6132,31 +6424,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>343</v>
+        <v>418</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
@@ -6164,31 +6456,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>419</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>186</v>
+        <v>420</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>172</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -6205,13 +6497,13 @@
         <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F9" s="3">
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
@@ -6228,31 +6520,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -6260,31 +6552,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>416</v>
+        <v>330</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>417</v>
+        <v>318</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F11" s="3">
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -6292,31 +6584,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3">
         <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
@@ -6324,31 +6616,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F13" s="3">
         <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -6356,31 +6648,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F14" s="3">
         <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15">
@@ -6388,28 +6680,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F15" s="3">
         <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>46</v>
@@ -6420,31 +6712,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>440</v>
+        <v>167</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>441</v>
+        <v>168</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>76</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17">
@@ -6452,31 +6744,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>174</v>
+        <v>456</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F17" s="3">
         <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -6484,31 +6776,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>58</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19">
@@ -6516,31 +6808,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>341</v>
+        <v>464</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>398</v>
+        <v>466</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -6548,31 +6840,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>457</v>
+        <v>365</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>196</v>
+        <v>469</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
@@ -6580,31 +6872,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>461</v>
+        <v>207</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>307</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W37.xlsx
+++ b/reports/devops-jobs-israel-2026-W37.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="494">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10T11:08:11</t>
+    <t xml:space="preserve">2026-09-11T11:07:47</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -435,1015 +435,1015 @@
     <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NextSilicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463560903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Infrastructure Specialist (37551)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-specialist-37551-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4465650418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBX Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - 5671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-5671-at-entrypoint-4464516580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senior devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terra Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comply365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infrastructure Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infrastructure-tech-lead-at-sunbit-4464526695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
     <t xml:space="preserve">Upwind Security</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463554987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4461933489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-ai-4462268859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4461835218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBX Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Autonomous Workspace Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comply365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terra Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer ( Kafka Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-kafka-oriented-at-nuvei-4464020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure Team Leader- 243578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-team-leader-243578-at-experis-4463040596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextSilicon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1464,13 +1464,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1622,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1646,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>993</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="10">
@@ -1718,7 +1721,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1745,31 +1748,31 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1782,7 +1785,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1790,7 +1793,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1809,7 +1812,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>476</v>
@@ -1820,39 +1823,39 @@
         <v>477</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>478</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>478</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>383</v>
+        <v>479</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>479</v>
+        <v>380</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1860,7 +1863,7 @@
         <v>480</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1868,15 +1871,15 @@
         <v>481</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1884,44 +1887,44 @@
         <v>482</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>378</v>
+        <v>483</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>483</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -1929,7 +1932,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>376</v>
+        <v>484</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -1957,13 +1960,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2">
@@ -1974,10 +1977,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>14.7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1986,88 +1989,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>34.2</v>
+        <v>35.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.1</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.0</v>
+        <v>16.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.8</v>
+        <v>21.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2079,7 +2082,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2151,7 +2154,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2186,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2215,7 +2218,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -2247,7 +2250,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2277,7 +2280,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2309,7 +2312,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2341,7 +2344,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2373,7 +2376,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -2405,7 +2408,7 @@
         <v>58</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2437,7 +2440,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -2469,7 +2472,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -2501,7 +2504,7 @@
         <v>85</v>
       </c>
       <c r="J13" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -2533,7 +2536,7 @@
         <v>89</v>
       </c>
       <c r="J14" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -2565,7 +2568,7 @@
         <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -2597,7 +2600,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -2629,7 +2632,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -2661,7 +2664,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -2693,7 +2696,7 @@
         <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -2725,7 +2728,7 @@
         <v>93</v>
       </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2757,7 +2760,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2789,7 +2792,7 @@
         <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -2821,7 +2824,7 @@
         <v>128</v>
       </c>
       <c r="J23" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -2853,7 +2856,7 @@
         <v>65</v>
       </c>
       <c r="J24" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -2885,7 +2888,7 @@
         <v>138</v>
       </c>
       <c r="J25" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2917,7 +2920,7 @@
         <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -2949,7 +2952,7 @@
         <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2981,7 +2984,7 @@
         <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -3013,7 +3016,7 @@
         <v>78</v>
       </c>
       <c r="J29" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -3045,7 +3048,7 @@
         <v>161</v>
       </c>
       <c r="J30" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -3077,81 +3080,81 @@
         <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D32" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J32" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D33" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="J33" s="3">
-        <v>87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>37</v>
@@ -3161,54 +3164,54 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>43</v>
@@ -3221,30 +3224,30 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3254,21 +3257,21 @@
         <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="J37" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>135</v>
@@ -3281,30 +3284,30 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="J38" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3314,84 +3317,84 @@
         <v>194</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="J40" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>48</v>
@@ -3401,54 +3404,56 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="J42" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>43</v>
@@ -3456,9 +3461,7 @@
       <c r="E44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
@@ -3466,54 +3469,54 @@
         <v>214</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J45" s="3">
-        <v>25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>48</v>
@@ -3526,10 +3529,10 @@
         <v>221</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="J46" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -3537,10 +3540,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>43</v>
@@ -3553,24 +3556,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
@@ -3583,13 +3586,13 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J48" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
@@ -3597,10 +3600,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>43</v>
@@ -3613,24 +3616,24 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>43</v>
@@ -3649,21 +3652,21 @@
         <v>58</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>48</v>
@@ -3673,24 +3676,24 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="J51" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>43</v>
@@ -3703,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3717,10 +3720,10 @@
         <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>43</v>
@@ -3733,84 +3736,84 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>43</v>
@@ -3823,54 +3826,54 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>249</v>
+        <v>56</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>251</v>
+        <v>179</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
@@ -3883,114 +3886,114 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>47</v>
+        <v>261</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>43</v>
@@ -4003,10 +4006,10 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="J62" s="3">
         <v>1</v>
@@ -4014,46 +4017,46 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>269</v>
+        <v>47</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>48</v>
@@ -4063,59 +4066,57 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>171</v>
+        <v>273</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4125,27 +4126,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>182</v>
+        <v>276</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>48</v>
@@ -4155,87 +4156,89 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>204</v>
+        <v>281</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>94</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F69" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="J69" s="3">
-        <v>87</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>48</v>
@@ -4245,24 +4248,24 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="J70" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>202</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>43</v>
@@ -4275,30 +4278,30 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>293</v>
+        <v>169</v>
       </c>
       <c r="J71" s="3">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4308,10 +4311,10 @@
         <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="J72" s="3">
-        <v>21</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73">
@@ -4322,13 +4325,13 @@
         <v>297</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>168</v>
+        <v>285</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -4338,54 +4341,54 @@
         <v>298</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J74" s="3">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4398,10 +4401,10 @@
         <v>305</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -4412,13 +4415,13 @@
         <v>307</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
@@ -4428,21 +4431,21 @@
         <v>308</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>309</v>
+        <v>169</v>
       </c>
       <c r="J76" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>310</v>
+        <v>158</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>43</v>
@@ -4455,27 +4458,27 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>192</v>
+        <v>312</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>313</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4488,54 +4491,54 @@
         <v>314</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>233</v>
+        <v>315</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4545,40 +4548,40 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>47</v>
+        <v>322</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -4586,16 +4589,16 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4605,10 +4608,10 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="J82" s="3">
         <v>2</v>
@@ -4616,13 +4619,13 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>323</v>
+        <v>41</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>43</v>
@@ -4631,30 +4634,30 @@
         <v>37</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>36</v>
@@ -4667,27 +4670,27 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
@@ -4697,43 +4700,43 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J85" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>333</v>
+        <v>202</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>217</v>
+        <v>65</v>
       </c>
       <c r="J86" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87">
@@ -4741,13 +4744,13 @@
         <v>47</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>48</v>
@@ -4757,84 +4760,84 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J87" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>204</v>
+        <v>332</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="J89" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>233</v>
+        <v>343</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>43</v>
@@ -4847,89 +4850,87 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>293</v>
+        <v>58</v>
       </c>
       <c r="J90" s="3">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>182</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>204</v>
+        <v>349</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>348</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="J92" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>352</v>
+        <v>175</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>48</v>
@@ -4942,21 +4943,21 @@
         <v>353</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>354</v>
+        <v>138</v>
       </c>
       <c r="J93" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>43</v>
@@ -4969,54 +4970,54 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>89</v>
       </c>
       <c r="J94" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>361</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>43</v>
@@ -5029,24 +5030,24 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>43</v>
@@ -5059,27 +5060,27 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>37</v>
@@ -5092,27 +5093,27 @@
         <v>367</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>47</v>
+        <v>368</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>369</v>
+        <v>175</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
@@ -5122,44 +5123,14 @@
         <v>370</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J100" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5259,7 +5230,6 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5267,8 +5237,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5301,13 +5271,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5315,37 +5285,37 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>175</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5353,18 +5323,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5372,18 +5342,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5391,18 +5361,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5410,18 +5380,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5429,18 +5399,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>318</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5448,18 +5418,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>351</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5467,18 +5437,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5486,68 +5456,11 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5559,9 +5472,6 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5575,15 +5485,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5591,7 +5501,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5599,7 +5509,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5607,7 +5517,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="B5" s="3">
         <v>20</v>
@@ -5615,7 +5525,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5623,7 +5533,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5631,7 +5541,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5639,7 +5549,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5647,7 +5557,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5663,7 +5573,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5671,7 +5581,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5679,7 +5589,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5687,7 +5597,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5695,7 +5605,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5717,7 +5627,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5730,15 +5640,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5746,7 +5656,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5754,7 +5664,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5762,7 +5672,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5770,7 +5680,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5778,15 +5688,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5794,7 +5704,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5802,7 +5712,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5810,7 +5720,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5818,7 +5728,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5826,7 +5736,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5834,7 +5744,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>241</v>
+        <v>332</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5855,16 +5765,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5956,13 +5866,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5970,13 +5880,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C9" s="3">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5984,10 +5894,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -5998,13 +5908,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6012,7 +5922,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -6026,7 +5936,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6068,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6094,21 +6004,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -6116,10 +6026,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -6130,7 +6040,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6149,7 +6059,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -6157,7 +6067,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -6165,15 +6075,15 @@
         <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6186,7 +6096,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6194,7 +6104,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6229,10 +6139,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6244,10 +6154,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6264,28 +6174,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>89</v>
@@ -6296,31 +6206,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
@@ -6328,31 +6238,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>243</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
@@ -6360,31 +6270,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>185</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -6392,31 +6302,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -6424,31 +6334,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>363</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>242</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>418</v>
+        <v>39</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -6456,31 +6366,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F8" s="3">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F8" s="3">
-        <v>84</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -6488,19 +6398,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>421</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>35</v>
+        <v>422</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>423</v>
@@ -6509,10 +6419,10 @@
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>39</v>
+        <v>424</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>40</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10">
@@ -6520,31 +6430,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -6552,31 +6462,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>428</v>
+        <v>359</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>330</v>
+        <v>431</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6584,31 +6494,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>433</v>
+        <v>241</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>170</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13">
@@ -6616,31 +6526,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="F13" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
@@ -6648,31 +6558,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>443</v>
+        <v>189</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>446</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -6680,31 +6590,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>365</v>
+        <v>448</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>352</v>
+        <v>450</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6712,31 +6622,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>450</v>
+        <v>359</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>167</v>
+        <v>453</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>453</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -6744,19 +6654,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>455</v>
+        <v>205</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>456</v>
+        <v>285</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>457</v>
@@ -6782,13 +6692,13 @@
         <v>460</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>438</v>
+        <v>399</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>461</v>
@@ -6800,7 +6710,7 @@
         <v>462</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>463</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -6808,31 +6718,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F19" s="3">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F19" s="3">
+      <c r="J19" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -6840,31 +6750,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>365</v>
+        <v>467</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F20" s="3">
+        <v>28</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F20" s="3">
-        <v>44</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
@@ -6872,19 +6782,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>473</v>
@@ -6896,7 +6806,7 @@
         <v>474</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W37.xlsx
+++ b/reports/devops-jobs-israel-2026-W37.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-11T11:07:47</t>
+    <t xml:space="preserve">2026-09-13T11:39:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -609,6 +609,15 @@
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sr. DevOps Engineer</t>
   </si>
   <si>
@@ -660,15 +669,6 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
@@ -696,42 +696,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
   </si>
   <si>
     <t xml:space="preserve">DriveNets</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
   </si>
   <si>
@@ -762,6 +753,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
   </si>
   <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer - 5671</t>
   </si>
   <si>
@@ -771,12 +783,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-5671-at-entrypoint-4464516580</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4461841163</t>
-  </si>
-  <si>
     <t xml:space="preserve">Integress, Inc.</t>
   </si>
   <si>
@@ -792,27 +798,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-autonomous-workspace-platform-at-check-point-software-4464032419</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Tech Lead</t>
   </si>
   <si>
@@ -840,445 +825,442 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+    <t xml:space="preserve">DevOps / SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miggo Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senior devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4462202795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terra Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infrastructure Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infrastructure-tech-lead-at-sunbit-4464526695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">senior devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sela-4461833294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP-Cloud DevOps engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-cloud-devops-engineer-at-commit-4461815980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AITAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer – Datastores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-%E2%80%93-datastores-at-coralogix-4464350962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terra Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-ai-4462263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4464337565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comply365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infrastructure Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infrastructure-tech-lead-at-sunbit-4464526695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Production Operations Engineer</t>
@@ -1314,15 +1296,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -1365,21 +1338,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
-  </si>
-  <si>
     <t xml:space="preserve">TytoCare</t>
   </si>
   <si>
@@ -1410,21 +1368,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1446,6 +1404,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1455,25 +1440,19 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1625,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -1633,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1641,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1649,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1003</v>
+        <v>976</v>
       </c>
     </row>
     <row r="10">
@@ -1721,7 +1700,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1748,36 +1727,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>428</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1785,7 +1764,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1793,7 +1772,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1806,69 +1785,69 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>474</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>479</v>
+        <v>365</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>481</v>
+        <v>369</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -1876,66 +1855,66 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>482</v>
+        <v>359</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>476</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>483</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1960,13 +1939,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
@@ -1977,10 +1956,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>14.7</v>
+        <v>14.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1989,88 +1968,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.7</v>
+        <v>8.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.0</v>
+        <v>34.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2154,7 +2133,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -2186,7 +2165,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2218,7 +2197,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -2250,7 +2229,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -2280,7 +2259,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2312,7 +2291,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2344,7 +2323,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2376,7 +2355,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -2408,7 +2387,7 @@
         <v>58</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2440,7 +2419,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -2472,7 +2451,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2504,7 +2483,7 @@
         <v>85</v>
       </c>
       <c r="J13" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -2536,7 +2515,7 @@
         <v>89</v>
       </c>
       <c r="J14" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -2568,7 +2547,7 @@
         <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -2600,7 +2579,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -2632,7 +2611,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -2664,7 +2643,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -2696,7 +2675,7 @@
         <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -2728,7 +2707,7 @@
         <v>93</v>
       </c>
       <c r="J20" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2760,7 +2739,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2792,7 +2771,7 @@
         <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -2824,7 +2803,7 @@
         <v>128</v>
       </c>
       <c r="J23" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -2856,7 +2835,7 @@
         <v>65</v>
       </c>
       <c r="J24" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -2888,7 +2867,7 @@
         <v>138</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2920,7 +2899,7 @@
         <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2952,7 +2931,7 @@
         <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2984,7 +2963,7 @@
         <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
@@ -3016,7 +2995,7 @@
         <v>78</v>
       </c>
       <c r="J29" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -3048,7 +3027,7 @@
         <v>161</v>
       </c>
       <c r="J30" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -3080,7 +3059,7 @@
         <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -3110,7 +3089,7 @@
         <v>169</v>
       </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -3140,7 +3119,7 @@
         <v>58</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3170,7 +3149,7 @@
         <v>138</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3200,7 +3179,7 @@
         <v>169</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -3230,7 +3209,7 @@
         <v>169</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -3260,7 +3239,7 @@
         <v>149</v>
       </c>
       <c r="J37" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -3290,7 +3269,7 @@
         <v>138</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3320,21 +3299,21 @@
         <v>195</v>
       </c>
       <c r="J39" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>48</v>
@@ -3344,27 +3323,27 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="J40" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>48</v>
@@ -3377,10 +3356,10 @@
         <v>203</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="J41" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -3391,10 +3370,10 @@
         <v>205</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>48</v>
@@ -3404,56 +3383,54 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>43</v>
@@ -3461,7 +3438,9 @@
       <c r="E44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
@@ -3472,7 +3451,7 @@
         <v>215</v>
       </c>
       <c r="J44" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3502,7 +3481,7 @@
         <v>218</v>
       </c>
       <c r="J45" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
@@ -3532,7 +3511,7 @@
         <v>222</v>
       </c>
       <c r="J46" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -3562,15 +3541,15 @@
         <v>149</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>171</v>
@@ -3586,21 +3565,21 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="J48" s="3">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>171</v>
@@ -3616,10 +3595,10 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="J49" s="3">
         <v>3</v>
@@ -3627,16 +3606,16 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>48</v>
@@ -3646,27 +3625,27 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>48</v>
@@ -3679,18 +3658,18 @@
         <v>234</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="J51" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>171</v>
@@ -3706,13 +3685,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3720,10 +3699,10 @@
         <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>43</v>
@@ -3739,40 +3718,40 @@
         <v>239</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -3780,10 +3759,10 @@
         <v>179</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>43</v>
@@ -3796,13 +3775,13 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J55" s="3">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56">
@@ -3810,13 +3789,13 @@
         <v>179</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3826,24 +3805,24 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="J56" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>247</v>
+        <v>179</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>43</v>
@@ -3856,10 +3835,10 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3870,10 +3849,10 @@
         <v>179</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
@@ -3886,60 +3865,60 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>47</v>
+        <v>251</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>253</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
@@ -3949,10 +3928,10 @@
         <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3960,13 +3939,13 @@
         <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>37</v>
@@ -3976,21 +3955,21 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>171</v>
@@ -4006,21 +3985,21 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>171</v>
@@ -4036,57 +4015,57 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>47</v>
+        <v>264</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4096,173 +4075,173 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>274</v>
+        <v>189</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>276</v>
+        <v>149</v>
       </c>
       <c r="J66" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>287</v>
-      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>289</v>
+        <v>41</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>138</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>171</v>
@@ -4278,13 +4257,13 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -4292,7 +4271,7 @@
         <v>94</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>171</v>
@@ -4308,27 +4287,27 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J72" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>48</v>
@@ -4338,21 +4317,21 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J73" s="3">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>171</v>
@@ -4361,31 +4340,31 @@
         <v>43</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>303</v>
+        <v>89</v>
       </c>
       <c r="J74" s="3">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>43</v>
@@ -4398,24 +4377,24 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="J75" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>306</v>
+        <v>158</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>43</v>
@@ -4428,21 +4407,21 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>169</v>
+        <v>300</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>158</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>171</v>
@@ -4458,57 +4437,57 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="J77" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>312</v>
+        <v>52</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>171</v>
+        <v>308</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>37</v>
@@ -4518,27 +4497,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>199</v>
+        <v>313</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4548,27 +4527,27 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>37</v>
@@ -4578,27 +4557,27 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4608,21 +4587,21 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>327</v>
+        <v>205</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>171</v>
@@ -4631,90 +4610,88 @@
         <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>328</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>280</v>
+        <v>52</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>189</v>
+        <v>266</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>135</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>171</v>
@@ -4723,88 +4700,88 @@
         <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="J86" s="3">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>47</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="J87" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>171</v>
@@ -4813,61 +4790,61 @@
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>138</v>
+        <v>292</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>182</v>
+        <v>338</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>43</v>
@@ -4880,51 +4857,51 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>303</v>
+        <v>138</v>
       </c>
       <c r="J91" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>175</v>
@@ -4933,88 +4910,88 @@
         <v>43</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="J94" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="J95" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>175</v>
@@ -5030,107 +5007,17 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J97" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J98" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J99" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J96"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5227,9 +5114,6 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5237,8 +5121,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5271,32 +5155,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5304,18 +5188,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5323,18 +5207,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5342,18 +5226,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>289</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5361,117 +5245,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5485,15 +5269,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5501,7 +5285,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5509,7 +5293,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5517,7 +5301,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="B5" s="3">
         <v>20</v>
@@ -5525,7 +5309,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5533,7 +5317,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5541,15 +5325,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5557,7 +5341,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5573,7 +5357,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5581,7 +5365,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5589,7 +5373,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5597,7 +5381,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5605,7 +5389,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5627,7 +5411,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5672,7 +5456,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5680,7 +5464,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5704,7 +5488,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5712,7 +5496,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5720,7 +5504,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5728,7 +5512,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>226</v>
+        <v>317</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5736,18 +5520,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>332</v>
+        <v>124</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5765,16 +5549,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5880,7 +5664,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5894,7 +5678,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5908,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="C11" s="3">
         <v>2.8</v>
@@ -5922,13 +5706,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5936,13 +5720,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5950,13 +5734,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5964,13 +5748,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5978,7 +5762,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>177</v>
+        <v>317</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6004,21 +5788,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -6026,10 +5810,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -6037,10 +5821,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +5843,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -6067,7 +5851,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -6075,15 +5859,15 @@
         <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>286</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6091,28 +5875,28 @@
         <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>313</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6127,7 +5911,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6139,10 +5923,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6154,10 +5938,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6174,28 +5958,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>89</v>
@@ -6206,31 +5990,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4">
@@ -6238,31 +6022,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>409</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -6270,31 +6054,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>359</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>360</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="F5" s="3">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>361</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -6302,31 +6086,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7">
@@ -6334,31 +6118,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>403</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>405</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>407</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>408</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>40</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
@@ -6366,31 +6150,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>171</v>
+        <v>308</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>276</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -6398,31 +6182,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F9" s="3">
         <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10">
@@ -6430,28 +6214,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="F10" s="3">
         <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>78</v>
@@ -6462,31 +6246,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="F11" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12">
@@ -6494,31 +6278,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>438</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -6526,31 +6310,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -6558,31 +6342,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>443</v>
+        <v>344</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="F14" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -6590,31 +6374,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>449</v>
+        <v>208</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>450</v>
+        <v>312</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F15" s="3">
         <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -6622,31 +6406,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>359</v>
+        <v>445</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>184</v>
+        <v>266</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -6654,31 +6438,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>450</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>82</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18">
@@ -6686,28 +6470,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F18" s="3">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>89</v>
@@ -6718,31 +6502,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>359</v>
+        <v>457</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>464</v>
+        <v>255</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -6750,31 +6534,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>468</v>
+        <v>223</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>89</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21">
@@ -6782,31 +6566,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>253</v>
+        <v>467</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
